--- a/results/CA/node2vec_embedding_size_results.xlsx
+++ b/results/CA/node2vec_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.827099895570052</v>
+        <v>0.821392544573845</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8287553635732765</v>
+        <v>0.8246374502895607</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8315393547248536</v>
+        <v>0.8275783434897879</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8334418022651334</v>
+        <v>0.8287054853617184</v>
       </c>
     </row>
   </sheetData>

--- a/results/CA/node2vec_embedding_size_results.xlsx
+++ b/results/CA/node2vec_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.821392544573845</v>
+        <v>0.8217237581504543</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8246374502895607</v>
+        <v>0.827069584515469</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8275783434897879</v>
+        <v>0.8253756278331614</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8287054853617184</v>
+        <v>0.8279961292922629</v>
       </c>
     </row>
   </sheetData>

--- a/results/CA/node2vec_embedding_size_results.xlsx
+++ b/results/CA/node2vec_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8217237581504543</v>
+        <v>0.8137207568131652</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.827069584515469</v>
+        <v>0.8085869699710677</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8253756278331614</v>
+        <v>0.8028797298324953</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8279961292922629</v>
+        <v>0.7943687776226794</v>
       </c>
     </row>
   </sheetData>

--- a/results/CA/node2vec_embedding_size_results.xlsx
+++ b/results/CA/node2vec_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8137207568131652</v>
+        <v>0.8127884496396487</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8085869699710677</v>
+        <v>0.8081658584506826</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8028797298324953</v>
+        <v>0.8017371489627125</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7943687776226794</v>
+        <v>0.7940663138089932</v>
       </c>
     </row>
   </sheetData>

--- a/results/CA/node2vec_embedding_size_results.xlsx
+++ b/results/CA/node2vec_embedding_size_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8127884496396487</v>
+        <v>0.8136967034193967</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8081658584506826</v>
+        <v>0.8053713569815329</v>
       </c>
     </row>
     <row r="4">
@@ -461,15 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8017371489627125</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.7940663138089932</v>
+        <v>0.7991933318296518</v>
       </c>
     </row>
   </sheetData>

--- a/results/CA/node2vec_embedding_size_results.xlsx
+++ b/results/CA/node2vec_embedding_size_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8136967034193967</v>
+        <v>0.8178111965684268</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8053713569815329</v>
+        <v>0.8217020984860509</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,15 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7991933318296518</v>
+        <v>0.8221534307890822</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.8200591354186516</v>
       </c>
     </row>
   </sheetData>

--- a/results/CA/node2vec_embedding_size_results.xlsx
+++ b/results/CA/node2vec_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8178111965684268</v>
+        <v>0.8160620681335604</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8217020984860509</v>
+        <v>0.8199499610719225</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8221534307890822</v>
+        <v>0.8191776409226718</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8200591354186516</v>
+        <v>0.8162256750871931</v>
       </c>
     </row>
   </sheetData>

--- a/results/CA/node2vec_embedding_size_results.xlsx
+++ b/results/CA/node2vec_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8160620681335604</v>
+        <v>0.827099895570052</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8199499610719225</v>
+        <v>0.8287553635732765</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8191776409226718</v>
+        <v>0.8315393547248536</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8162256750871931</v>
+        <v>0.8334418022651334</v>
       </c>
     </row>
   </sheetData>

--- a/results/CA/node2vec_embedding_size_results.xlsx
+++ b/results/CA/node2vec_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.827099895570052</v>
+        <v>0.8276894033481159</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8287553635732765</v>
+        <v>0.8317516558592084</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8315393547248536</v>
+        <v>0.8298271445444685</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8334418022651334</v>
+        <v>0.8346348670403714</v>
       </c>
     </row>
   </sheetData>

--- a/results/CA/node2vec_embedding_size_results.xlsx
+++ b/results/CA/node2vec_embedding_size_results.xlsx
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8276894033481159</v>
+        <v>0.8160620681335604</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8317516558592084</v>
+        <v>0.8199499610719225</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8298271445444685</v>
+        <v>0.8191776409226718</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8346348670403714</v>
+        <v>0.8162256750871931</v>
       </c>
     </row>
   </sheetData>

--- a/results/CA/node2vec_embedding_size_results.xlsx
+++ b/results/CA/node2vec_embedding_size_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8160620681335604</v>
+        <v>0.818396181190268</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8199499610719225</v>
+        <v>0.8187935816775302</v>
       </c>
     </row>
     <row r="4">
@@ -461,15 +461,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8191776409226718</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.8162256750871931</v>
+        <v>0.8218576236368522</v>
       </c>
     </row>
   </sheetData>

--- a/results/CA/node2vec_embedding_size_results.xlsx
+++ b/results/CA/node2vec_embedding_size_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0.818396181190268</v>
+        <v>0.8155093203020414</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8187935816775302</v>
+        <v>0.8213039304477124</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,15 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8218576236368522</v>
+        <v>0.8204871808013507</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.8220089954832307</v>
       </c>
     </row>
   </sheetData>
